--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/NEW_MEXICO_2022.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/NEW_MEXICO_2022.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D579"/>
+  <dimension ref="A1:D573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Asientos</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Cosío</t>
@@ -430,10 +445,15 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -447,9 +467,14 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C7">
@@ -460,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C8">
@@ -473,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San José de Gracia</t>
+          <t>San José De Gracia</t>
         </is>
       </c>
       <c r="C9">
@@ -486,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Tepezalá</t>
@@ -499,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -530,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Mexicali</t>
@@ -543,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -556,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -587,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Mulegé</t>
@@ -600,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Carmen</t>
@@ -640,10 +715,15 @@
         <v>3</v>
       </c>
       <c r="D20">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Champotón</t>
@@ -657,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -677,7 +762,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C23">
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -701,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Chanal</t>
@@ -723,10 +823,15 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Chiapilla</t>
@@ -740,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C28">
@@ -753,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Copainalá</t>
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -779,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Jiquipilas</t>
@@ -805,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -831,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -844,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ocozocoautla de Espinosa</t>
+          <t>Ocozocoautla De Espinosa</t>
         </is>
       </c>
       <c r="C36">
@@ -857,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -883,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -896,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -909,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -922,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -935,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Villa Corzo</t>
@@ -961,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -992,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Aldama</t>
@@ -1005,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -1018,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Aquiles Serdán</t>
@@ -1031,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Ascensión</t>
@@ -1044,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Bachíniva</t>
@@ -1057,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Balleza</t>
@@ -1070,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Batopilas</t>
@@ -1083,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Bocoyna</t>
@@ -1096,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Buenaventura</t>
@@ -1109,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Camargo</t>
@@ -1122,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Carichí</t>
@@ -1135,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Casas Grandes</t>
@@ -1148,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -1161,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Chínipas</t>
@@ -1174,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Coyame del Sotol</t>
+          <t>Coyame Del Sotol</t>
         </is>
       </c>
       <c r="C61">
@@ -1187,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1200,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Cusihuiriachi</t>
@@ -1213,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -1226,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Dr. Belisario Domínguez</t>
@@ -1239,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>El Tule</t>
@@ -1252,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Galeana</t>
@@ -1261,10 +1561,15 @@
         <v>3</v>
       </c>
       <c r="D67">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -1278,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Gran Morelos</t>
@@ -1291,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Guachochi</t>
@@ -1304,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -1317,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Guadalupe y Calvo</t>
+          <t>Guadalupe Y Calvo</t>
         </is>
       </c>
       <c r="C72">
@@ -1330,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Guerrero</t>
@@ -1343,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C74">
@@ -1356,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Huejotitán</t>
@@ -1369,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Ignacio Zaragoza</t>
@@ -1382,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Janos</t>
@@ -1395,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -1408,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -1421,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Julimes</t>
@@ -1430,10 +1795,15 @@
         <v>3</v>
       </c>
       <c r="D80">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>La Cruz</t>
@@ -1447,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -1460,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Manuel Benavides</t>
@@ -1473,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Matachí</t>
@@ -1486,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Meoqui</t>
@@ -1499,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Moris</t>
@@ -1512,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -1525,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Nonoava</t>
@@ -1538,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -1551,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1564,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Ojinaga</t>
@@ -1577,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Praxedis G. Guerrero</t>
@@ -1586,10 +2011,15 @@
         <v>3</v>
       </c>
       <c r="D92">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Riva Palacio</t>
@@ -1603,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Rosales</t>
@@ -1616,32 +2051,47 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>San Francisco de Borja</t>
+          <t>San Francisco De Borja</t>
         </is>
       </c>
       <c r="C95">
         <v>3</v>
       </c>
       <c r="D95">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>San Francisco del Oro</t>
+          <t>San Francisco Del Oro</t>
         </is>
       </c>
       <c r="C96">
         <v>3</v>
       </c>
       <c r="D96">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Santa Bárbara</t>
@@ -1655,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Santa Isabel</t>
@@ -1668,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Satevó</t>
@@ -1681,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -1694,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Temósachic</t>
@@ -1707,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Urique</t>
@@ -1720,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Uruachi</t>
@@ -1733,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Valle de Zaragoza</t>
+          <t>Valle De Zaragoza</t>
         </is>
       </c>
       <c r="C104">
@@ -1746,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1777,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -1790,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Monclova</t>
@@ -1803,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Múzquiz</t>
@@ -1816,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1829,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -1838,10 +2353,15 @@
         <v>3</v>
       </c>
       <c r="D111">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>San Pedro</t>
@@ -1851,10 +2371,15 @@
         <v>3</v>
       </c>
       <c r="D112">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1868,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Viesca</t>
@@ -1881,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1912,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Ixtlahuacán</t>
@@ -1925,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -1938,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1951,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1966,7 +2521,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -1978,10 +2533,15 @@
         <v>3</v>
       </c>
       <c r="D121">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1995,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -2008,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cuajimalpa de Morelos</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C124">
@@ -2021,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -2034,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -2047,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -2060,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -2073,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -2086,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -2099,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Milpa Alta</t>
@@ -2112,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -2125,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -2138,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -2151,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2182,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Canelas</t>
@@ -2195,9 +2825,14 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Coneto de Comonfort</t>
+          <t>Coneto De Comonfort</t>
         </is>
       </c>
       <c r="C138">
@@ -2208,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Cuencamé</t>
@@ -2221,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -2234,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -2247,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -2260,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -2273,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Guanaceví</t>
@@ -2286,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -2299,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Indé</t>
@@ -2312,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -2325,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -2338,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Mezquital</t>
@@ -2351,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Nazas</t>
@@ -2364,9 +3059,14 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Nombre de Dios</t>
+          <t>Nombre De Dios</t>
         </is>
       </c>
       <c r="C151">
@@ -2377,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Nuevo Ideal</t>
@@ -2390,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -2403,19 +3113,29 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Pánuco de Coronado</t>
+          <t>Pánuco De Coronado</t>
         </is>
       </c>
       <c r="C154">
         <v>3</v>
       </c>
       <c r="D154">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Poanas</t>
@@ -2429,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -2438,10 +3163,15 @@
         <v>3</v>
       </c>
       <c r="D156">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Rodeo</t>
@@ -2455,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>San Bernardo</t>
@@ -2468,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>San Dimas</t>
@@ -2481,9 +3221,14 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>San Juan de Guadalupe</t>
+          <t>San Juan De Guadalupe</t>
         </is>
       </c>
       <c r="C160">
@@ -2494,22 +3239,32 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C161">
         <v>3</v>
       </c>
       <c r="D161">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>San Luis del Cordero</t>
+          <t>San Luis Del Cordero</t>
         </is>
       </c>
       <c r="C162">
@@ -2520,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>San Pedro del Gallo</t>
+          <t>San Pedro Del Gallo</t>
         </is>
       </c>
       <c r="C163">
@@ -2533,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Santa Clara</t>
@@ -2546,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Santiago Papasquiaro</t>
@@ -2559,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Súchil</t>
@@ -2568,10 +3343,15 @@
         <v>3</v>
       </c>
       <c r="D166">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Tamazula</t>
@@ -2581,10 +3361,15 @@
         <v>3</v>
       </c>
       <c r="D167">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Tepehuanes</t>
@@ -2598,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Tlahualilo</t>
@@ -2611,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -2624,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2639,7 +3439,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -2655,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -2668,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Amecameca</t>
@@ -2681,9 +3491,14 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Atizapán de Zaragoza</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C175">
@@ -2694,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -2707,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Axapusco</t>
@@ -2720,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -2729,10 +3559,15 @@
         <v>3</v>
       </c>
       <c r="D178">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -2746,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -2759,9 +3599,14 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C181">
@@ -2772,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Huixquilucan</t>
@@ -2785,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C183">
@@ -2798,9 +3653,14 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ixtapan del Oro</t>
+          <t>Ixtapan Del Oro</t>
         </is>
       </c>
       <c r="C184">
@@ -2811,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -2820,13 +3685,18 @@
         <v>3</v>
       </c>
       <c r="D185">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C186">
@@ -2837,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -2850,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Nicolás Romero</t>
@@ -2863,9 +3743,14 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C189">
@@ -2876,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -2889,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -2902,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Teoloyucan</t>
@@ -2915,9 +3815,14 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C193">
@@ -2928,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -2941,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -2950,10 +3865,15 @@
         <v>3</v>
       </c>
       <c r="D195">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -2967,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Zumpahuacán</t>
@@ -2980,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3007,10 +3937,15 @@
         <v>3</v>
       </c>
       <c r="D199">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -3024,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -3037,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -3050,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Coroneo</t>
@@ -3063,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -3076,9 +4031,14 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C205">
@@ -3089,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -3102,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -3115,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>León</t>
@@ -3128,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -3141,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -3154,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -3167,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -3176,10 +4171,15 @@
         <v>3</v>
       </c>
       <c r="D212">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -3189,13 +4189,18 @@
         <v>3</v>
       </c>
       <c r="D213">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>San Diego de la Unión</t>
+          <t>San Diego De La Unión</t>
         </is>
       </c>
       <c r="C214">
@@ -3206,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -3219,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>San José Iturbide</t>
@@ -3232,9 +4247,14 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C217">
@@ -3245,9 +4265,14 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C218">
@@ -3258,9 +4283,14 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C219">
@@ -3271,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -3280,13 +4315,18 @@
         <v>3</v>
       </c>
       <c r="D220">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C221">
@@ -3297,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Villagrán</t>
@@ -3310,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -3323,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3343,7 +4398,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C225">
@@ -3354,9 +4409,14 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C226">
@@ -3367,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Apaxtla</t>
@@ -3380,9 +4445,14 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Atenango del Río</t>
+          <t>Atenango Del Río</t>
         </is>
       </c>
       <c r="C228">
@@ -3393,9 +4463,14 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C229">
@@ -3406,9 +4481,14 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C230">
@@ -3419,9 +4499,14 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C231">
@@ -3432,22 +4517,32 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C232">
         <v>3</v>
       </c>
       <c r="D232">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Cuetzala del Progreso</t>
+          <t>Cuetzala Del Progreso</t>
         </is>
       </c>
       <c r="C233">
@@ -3458,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -3471,9 +4571,14 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Ixcateopan de Cuauhtémoc</t>
+          <t>Ixcateopan De Cuauhtémoc</t>
         </is>
       </c>
       <c r="C235">
@@ -3484,9 +4589,14 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C236">
@@ -3497,9 +4607,14 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>La Unión de Isidoro Montes de Oca</t>
+          <t>La Unión De Isidoro Montes De Oca</t>
         </is>
       </c>
       <c r="C237">
@@ -3510,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -3523,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Mochitlán</t>
@@ -3536,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -3549,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -3562,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Pungarabato</t>
@@ -3575,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -3588,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -3601,9 +4751,14 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C245">
@@ -3614,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -3627,9 +4787,14 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C247">
@@ -3640,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -3653,9 +4823,14 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Tlalixtaquilla de Maldonado</t>
+          <t>Tlalixtaquilla De Maldonado</t>
         </is>
       </c>
       <c r="C249">
@@ -3666,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Xochistlahuaca</t>
@@ -3679,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3710,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -3723,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -3736,9 +4931,14 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Nopala de Villagrán</t>
+          <t>Nopala De Villagrán</t>
         </is>
       </c>
       <c r="C255">
@@ -3749,9 +4949,14 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C256">
@@ -3762,9 +4967,14 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Progreso de Obregón</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C257">
@@ -3775,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>San Salvador</t>
@@ -3788,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Singuilucan</t>
@@ -3801,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Tasquillo</t>
@@ -3814,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Tlanchinol</t>
@@ -3827,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Xochiatipan</t>
@@ -3840,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Xochicoatlán</t>
@@ -3853,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Yahualica</t>
@@ -3866,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -3879,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3910,9 +5165,14 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Atotonilco el Alto</t>
+          <t>Atotonilco El Alto</t>
         </is>
       </c>
       <c r="C268">
@@ -3923,19 +5183,29 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C269">
         <v>3</v>
       </c>
       <c r="D269">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Bolaños</t>
@@ -3949,9 +5219,14 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Cañadas de Obregón</t>
+          <t>Cañadas De Obregón</t>
         </is>
       </c>
       <c r="C271">
@@ -3962,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Chimaltitán</t>
@@ -3975,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Cihuatlán</t>
@@ -3988,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -4001,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -4014,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>El Grullo</t>
@@ -4027,9 +5327,14 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C277">
@@ -4040,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Etzatlán</t>
@@ -4053,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -4066,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Huejúcar</t>
@@ -4079,22 +5399,32 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Huejuquilla el Alto</t>
+          <t>Huejuquilla El Alto</t>
         </is>
       </c>
       <c r="C281">
         <v>3</v>
       </c>
       <c r="D281">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Ixtlahuacán de los Membrillos</t>
+          <t>Ixtlahuacán De Los Membrillos</t>
         </is>
       </c>
       <c r="C282">
@@ -4105,19 +5435,29 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Ixtlahuacán del Río</t>
+          <t>Ixtlahuacán Del Río</t>
         </is>
       </c>
       <c r="C283">
         <v>3</v>
       </c>
       <c r="D283">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -4131,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -4144,6 +5489,11 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -4157,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>Mascota</t>
@@ -4170,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Mezquitic</t>
@@ -4179,10 +5539,15 @@
         <v>3</v>
       </c>
       <c r="D288">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -4196,9 +5561,14 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>San Diego de Alejandría</t>
+          <t>San Diego De Alejandría</t>
         </is>
       </c>
       <c r="C290">
@@ -4209,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -4222,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>San Martín Hidalgo</t>
@@ -4235,9 +5615,14 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C293">
@@ -4248,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -4261,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -4274,9 +5669,14 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Teocuitatlán de Corona</t>
+          <t>Teocuitatlán De Corona</t>
         </is>
       </c>
       <c r="C296">
@@ -4287,19 +5687,29 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C297">
         <v>3</v>
       </c>
       <c r="D297">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Tlaquepaque</t>
@@ -4313,19 +5723,29 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C299">
         <v>3</v>
       </c>
       <c r="D299">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -4339,9 +5759,14 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Yahualica de González Gallo</t>
+          <t>Yahualica De González Gallo</t>
         </is>
       </c>
       <c r="C301">
@@ -4352,9 +5777,14 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Zacoalco de Torres</t>
+          <t>Zacoalco De Torres</t>
         </is>
       </c>
       <c r="C302">
@@ -4365,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -4378,9 +5813,14 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Zapotlán del Rey</t>
+          <t>Zapotlán Del Rey</t>
         </is>
       </c>
       <c r="C304">
@@ -4391,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -4404,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4435,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -4444,10 +5899,15 @@
         <v>3</v>
       </c>
       <c r="D308">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Aquila</t>
@@ -4461,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Arteaga</t>
@@ -4474,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Carácuaro</t>
@@ -4487,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -4500,9 +5975,14 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Cojumatlán de Régules</t>
+          <t>Cojumatlán De Régules</t>
         </is>
       </c>
       <c r="C313">
@@ -4513,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -4526,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -4539,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -4552,6 +6047,11 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -4561,10 +6061,15 @@
         <v>3</v>
       </c>
       <c r="D317">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -4578,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Madero</t>
@@ -4591,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -4604,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -4617,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -4630,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>Nocupétaro</t>
@@ -4643,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Nuevo Parangaricutiro</t>
@@ -4656,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Penjamillo</t>
@@ -4669,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -4682,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>Salvador Escalante</t>
@@ -4695,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -4704,10 +6259,15 @@
         <v>3</v>
       </c>
       <c r="D328">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>Tancítaro</t>
@@ -4721,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Tingüindín</t>
@@ -4734,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Tocumbo</t>
@@ -4747,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -4756,10 +6331,15 @@
         <v>3</v>
       </c>
       <c r="D332">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -4773,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Tzitzio</t>
@@ -4786,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -4799,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Villamar</t>
@@ -4812,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -4825,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -4838,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4869,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -4882,6 +6497,11 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -4895,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>Jiutepec</t>
@@ -4908,6 +6533,11 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -4921,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -4934,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>Temoac</t>
@@ -4947,9 +6587,14 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C347">
@@ -4960,6 +6605,11 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>Xochitepec</t>
@@ -4973,6 +6623,11 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -4986,9 +6641,14 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Zacualpan de Amilpas</t>
+          <t>Zacualpan De Amilpas</t>
         </is>
       </c>
       <c r="C350">
@@ -4999,6 +6659,11 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5030,9 +6695,14 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Amatlán de Cañas</t>
+          <t>Amatlán De Cañas</t>
         </is>
       </c>
       <c r="C353">
@@ -5043,9 +6713,14 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Bahía de Banderas</t>
+          <t>Bahía De Banderas</t>
         </is>
       </c>
       <c r="C354">
@@ -5056,6 +6731,11 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Compostela</t>
@@ -5069,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Huajicori</t>
@@ -5082,6 +6767,11 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -5091,23 +6781,33 @@
         <v>3</v>
       </c>
       <c r="D357">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Santa María del Oro</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C358">
         <v>3</v>
       </c>
       <c r="D358">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -5117,10 +6817,15 @@
         <v>3</v>
       </c>
       <c r="D359">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -5134,6 +6839,11 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5165,6 +6875,11 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -5178,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Linares</t>
@@ -5191,6 +6911,11 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -5204,6 +6929,11 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
           <t>Sabinas Hidalgo</t>
@@ -5217,9 +6947,14 @@
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C367">
@@ -5230,6 +6965,11 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5250,7 +6990,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C369">
@@ -5261,6 +7001,11 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
           <t>Ciudad Ixtepec</t>
@@ -5274,6 +7019,11 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
           <t>Concepción Buenavista</t>
@@ -5287,9 +7037,14 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Guevea de Humboldt</t>
+          <t>Guevea De Humboldt</t>
         </is>
       </c>
       <c r="C372">
@@ -5300,9 +7055,14 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C373">
@@ -5313,9 +7073,14 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Tlaxiaco</t>
+          <t>Heroica Ciudad De Tlaxiaco</t>
         </is>
       </c>
       <c r="C374">
@@ -5326,9 +7091,14 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C375">
@@ -5339,9 +7109,14 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C376">
@@ -5352,6 +7127,11 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -5361,13 +7141,18 @@
         <v>3</v>
       </c>
       <c r="D377">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C378">
@@ -5378,9 +7163,14 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C379">
@@ -5391,9 +7181,14 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C380">
@@ -5404,6 +7199,11 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
           <t>San Dionisio Ocotepec</t>
@@ -5417,6 +7217,11 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>San Francisco Cahuacuá</t>
@@ -5426,10 +7231,15 @@
         <v>3</v>
       </c>
       <c r="D382">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>San Ildefonso Villa Alta</t>
@@ -5443,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>San José Chiltepec</t>
@@ -5456,6 +7271,11 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
           <t>San Juan Bautista Atatlahuca</t>
@@ -5469,6 +7289,11 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
           <t>San Juan Bautista Coixtlahuaca</t>
@@ -5482,6 +7307,11 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -5495,6 +7325,11 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
           <t>San Juan Cotzocón</t>
@@ -5508,6 +7343,11 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
           <t>San Lucas Ojitlán</t>
@@ -5521,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>San Miguel Chicahua</t>
@@ -5534,9 +7379,14 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>San Miguel el Grande</t>
+          <t>San Miguel El Grande</t>
         </is>
       </c>
       <c r="C391">
@@ -5547,6 +7397,11 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>San Pedro Ixcatlán</t>
@@ -5560,6 +7415,11 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
           <t>San Pedro Jocotipac</t>
@@ -5573,6 +7433,11 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>San Pedro Quiatoni</t>
@@ -5586,6 +7451,11 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
           <t>San Pedro Totolapa</t>
@@ -5599,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -5612,6 +7487,11 @@
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
           <t>Santiago Amoltepec</t>
@@ -5625,6 +7505,11 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
           <t>Santiago Jocotepec</t>
@@ -5638,6 +7523,11 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -5651,6 +7541,11 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>Santiago Niltepec</t>
@@ -5664,6 +7559,11 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>Santo Tomás Mazaltepec</t>
@@ -5677,6 +7577,11 @@
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -5690,22 +7595,32 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Tepelmeme Villa de Morelos</t>
+          <t>Tepelmeme Villa De Morelos</t>
         </is>
       </c>
       <c r="C403">
         <v>3</v>
       </c>
       <c r="D403">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C404">
@@ -5716,6 +7631,11 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5747,6 +7667,11 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>Atexcal</t>
@@ -5760,6 +7685,11 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>Cañada Morelos</t>
@@ -5773,6 +7703,11 @@
       </c>
     </row>
     <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B409" t="inlineStr">
         <is>
           <t>Chiconcuautla</t>
@@ -5786,6 +7721,11 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -5799,6 +7739,11 @@
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
           <t>Cuautlancingo</t>
@@ -5812,9 +7757,14 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C412">
@@ -5825,6 +7775,11 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
           <t>Huauchinango</t>
@@ -5838,6 +7793,11 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
           <t>Hueyapan</t>
@@ -5847,13 +7807,18 @@
         <v>3</v>
       </c>
       <c r="D414">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C415">
@@ -5864,6 +7829,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>Nauzontla</t>
@@ -5877,6 +7847,11 @@
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -5890,6 +7865,11 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>Quecholac</t>
@@ -5903,6 +7883,11 @@
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -5916,9 +7901,14 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>San Nicolás de los Ranchos</t>
+          <t>San Nicolás De Los Ranchos</t>
         </is>
       </c>
       <c r="C420">
@@ -5929,6 +7919,11 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -5942,6 +7937,11 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -5955,9 +7955,14 @@
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C423">
@@ -5968,9 +7973,14 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Teteles de Avila Castillo</t>
+          <t>Teteles De Avila Castillo</t>
         </is>
       </c>
       <c r="C424">
@@ -5981,6 +7991,11 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -5994,6 +8009,11 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
           <t>Tlatlauquitepec</t>
@@ -6007,6 +8027,11 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
           <t>Tochtepec</t>
@@ -6020,6 +8045,11 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Tulcingo</t>
@@ -6029,10 +8059,15 @@
         <v>3</v>
       </c>
       <c r="D428">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -6046,6 +8081,11 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -6059,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -6072,6 +8117,11 @@
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6092,7 +8142,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C433">
@@ -6103,9 +8153,14 @@
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C434">
@@ -6116,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>Huimilpan</t>
@@ -6129,6 +8189,11 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -6142,6 +8207,11 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
           <t>San Joaquín</t>
@@ -6155,6 +8225,11 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6186,6 +8261,11 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6213,10 +8293,15 @@
         <v>3</v>
       </c>
       <c r="D441">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
           <t>Cerritos</t>
@@ -6230,9 +8315,14 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C443">
@@ -6243,6 +8333,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
           <t>Ciudad Fernández</t>
@@ -6256,6 +8351,11 @@
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -6269,6 +8369,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
           <t>Guadalcázar</t>
@@ -6282,6 +8387,11 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
           <t>Moctezuma</t>
@@ -6295,6 +8405,11 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -6308,6 +8423,11 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -6321,6 +8441,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -6334,6 +8459,11 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
           <t>Tamasopo</t>
@@ -6347,6 +8477,11 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
           <t>Tampamolón Corona</t>
@@ -6360,6 +8495,11 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
           <t>Tamuín</t>
@@ -6373,6 +8513,11 @@
       </c>
     </row>
     <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
           <t>Vanegas</t>
@@ -6386,9 +8531,14 @@
       </c>
     </row>
     <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Villa de Arriaga</t>
+          <t>Villa De Arriaga</t>
         </is>
       </c>
       <c r="C455">
@@ -6399,9 +8549,14 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Villa de Guadalupe</t>
+          <t>Villa De Guadalupe</t>
         </is>
       </c>
       <c r="C456">
@@ -6412,9 +8567,14 @@
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C457">
@@ -6425,9 +8585,14 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Villa de Reyes</t>
+          <t>Villa De Reyes</t>
         </is>
       </c>
       <c r="C458">
@@ -6438,6 +8603,11 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -6451,6 +8621,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Villa Juárez</t>
@@ -6464,6 +8639,11 @@
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -6477,6 +8657,11 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6508,6 +8693,11 @@
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
           <t>Choix</t>
@@ -6521,6 +8711,11 @@
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -6534,6 +8729,11 @@
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -6543,10 +8743,15 @@
         <v>3</v>
       </c>
       <c r="D466">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -6560,6 +8765,11 @@
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
           <t>Navolato</t>
@@ -6573,6 +8783,11 @@
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
           <t>Salvador Alvarado</t>
@@ -6586,6 +8801,11 @@
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6617,6 +8837,11 @@
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
           <t>Alamos</t>
@@ -6630,6 +8855,11 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
           <t>Arivechi</t>
@@ -6643,6 +8873,11 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
           <t>Bacerac</t>
@@ -6652,10 +8887,15 @@
         <v>3</v>
       </c>
       <c r="D474">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
           <t>Bácum</t>
@@ -6669,6 +8909,11 @@
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
           <t>Cajeme</t>
@@ -6682,6 +8927,11 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
           <t>Cananea</t>
@@ -6695,6 +8945,11 @@
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
           <t>Etchojoa</t>
@@ -6708,6 +8963,11 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -6721,6 +8981,11 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -6734,6 +8999,11 @@
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
           <t>Huatabampo</t>
@@ -6747,9 +9017,14 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Nacozari de García</t>
+          <t>Nacozari De García</t>
         </is>
       </c>
       <c r="C482">
@@ -6760,6 +9035,11 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
           <t>Navojoa</t>
@@ -6773,6 +9053,11 @@
       </c>
     </row>
     <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -6786,6 +9071,11 @@
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
           <t>Opodepe</t>
@@ -6799,6 +9089,11 @@
       </c>
     </row>
     <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B486" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -6812,6 +9107,11 @@
       </c>
     </row>
     <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B487" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6843,6 +9143,11 @@
       </c>
     </row>
     <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B489" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -6856,6 +9161,11 @@
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6865,7 +9175,7 @@
         <v>3</v>
       </c>
       <c r="D490">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="491">
@@ -6887,6 +9197,11 @@
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
           <t>Nuevo Laredo</t>
@@ -6900,6 +9215,11 @@
       </c>
     </row>
     <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B493" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -6913,9 +9233,14 @@
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Soto la Marina</t>
+          <t>Soto La Marina</t>
         </is>
       </c>
       <c r="C494">
@@ -6926,6 +9251,11 @@
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -6939,6 +9269,11 @@
       </c>
     </row>
     <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B496" t="inlineStr">
         <is>
           <t>Valle Hermoso</t>
@@ -6952,6 +9287,11 @@
       </c>
     </row>
     <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B497" t="inlineStr">
         <is>
           <t>Xicoténcatl</t>
@@ -6965,6 +9305,11 @@
       </c>
     </row>
     <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B498" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6985,7 +9330,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Apetatitlán de Antonio Carvajal</t>
+          <t>Apetatitlán De Antonio Carvajal</t>
         </is>
       </c>
       <c r="C499">
@@ -6996,6 +9341,11 @@
       </c>
     </row>
     <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
           <t>Apizaco</t>
@@ -7009,6 +9359,11 @@
       </c>
     </row>
     <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B501" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -7022,6 +9377,11 @@
       </c>
     </row>
     <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B502" t="inlineStr">
         <is>
           <t>Natívitas</t>
@@ -7035,6 +9395,11 @@
       </c>
     </row>
     <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B503" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -7044,10 +9409,15 @@
         <v>3</v>
       </c>
       <c r="D503">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B504" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -7061,6 +9431,11 @@
       </c>
     </row>
     <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B505" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7092,6 +9467,11 @@
       </c>
     </row>
     <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B507" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -7105,9 +9485,14 @@
       </c>
     </row>
     <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Alto Lucero de Gutiérrez Barrios</t>
+          <t>Alto Lucero De Gutiérrez Barrios</t>
         </is>
       </c>
       <c r="C508">
@@ -7118,6 +9503,11 @@
       </c>
     </row>
     <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B509" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -7131,6 +9521,11 @@
       </c>
     </row>
     <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B510" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -7144,6 +9539,11 @@
       </c>
     </row>
     <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B511" t="inlineStr">
         <is>
           <t>Chacaltianguis</t>
@@ -7153,10 +9553,15 @@
         <v>3</v>
       </c>
       <c r="D511">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B512" t="inlineStr">
         <is>
           <t>Chinameca</t>
@@ -7170,6 +9575,11 @@
       </c>
     </row>
     <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B513" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -7183,6 +9593,11 @@
       </c>
     </row>
     <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B514" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -7192,13 +9607,18 @@
         <v>3</v>
       </c>
       <c r="D514">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C515">
@@ -7209,6 +9629,11 @@
       </c>
     </row>
     <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B516" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -7222,6 +9647,11 @@
       </c>
     </row>
     <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B517" t="inlineStr">
         <is>
           <t>Cuichapa</t>
@@ -7235,6 +9665,11 @@
       </c>
     </row>
     <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B518" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -7248,6 +9683,11 @@
       </c>
     </row>
     <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B519" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -7261,9 +9701,14 @@
       </c>
     </row>
     <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Ixhuatlán del Café</t>
+          <t>Ixhuatlán Del Café</t>
         </is>
       </c>
       <c r="C520">
@@ -7274,6 +9719,11 @@
       </c>
     </row>
     <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B521" t="inlineStr">
         <is>
           <t>Ixtaczoquitlán</t>
@@ -7287,6 +9737,11 @@
       </c>
     </row>
     <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B522" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -7300,6 +9755,11 @@
       </c>
     </row>
     <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B523" t="inlineStr">
         <is>
           <t>Juan Rodríguez Clara</t>
@@ -7313,9 +9773,14 @@
       </c>
     </row>
     <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Juchique de Ferrer</t>
+          <t>Juchique De Ferrer</t>
         </is>
       </c>
       <c r="C524">
@@ -7326,9 +9791,14 @@
       </c>
     </row>
     <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Lerdo de Tejada</t>
+          <t>Lerdo De Tejada</t>
         </is>
       </c>
       <c r="C525">
@@ -7339,6 +9809,11 @@
       </c>
     </row>
     <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B526" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -7352,6 +9827,11 @@
       </c>
     </row>
     <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B527" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -7365,6 +9845,11 @@
       </c>
     </row>
     <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B528" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -7378,6 +9863,11 @@
       </c>
     </row>
     <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B529" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -7391,6 +9881,11 @@
       </c>
     </row>
     <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B530" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -7404,6 +9899,11 @@
       </c>
     </row>
     <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B531" t="inlineStr">
         <is>
           <t>Río Blanco</t>
@@ -7413,10 +9913,15 @@
         <v>3</v>
       </c>
       <c r="D531">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B532" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -7430,6 +9935,11 @@
       </c>
     </row>
     <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B533" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -7443,6 +9953,11 @@
       </c>
     </row>
     <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B534" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -7456,6 +9971,11 @@
       </c>
     </row>
     <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B535" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -7469,6 +9989,11 @@
       </c>
     </row>
     <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B536" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -7482,6 +10007,11 @@
       </c>
     </row>
     <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B537" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -7495,6 +10025,11 @@
       </c>
     </row>
     <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B538" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7526,6 +10061,11 @@
       </c>
     </row>
     <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B540" t="inlineStr">
         <is>
           <t>Mérida</t>
@@ -7539,6 +10079,11 @@
       </c>
     </row>
     <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B541" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7570,6 +10115,11 @@
       </c>
     </row>
     <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B543" t="inlineStr">
         <is>
           <t>Apulco</t>
@@ -7583,6 +10133,11 @@
       </c>
     </row>
     <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B544" t="inlineStr">
         <is>
           <t>Chalchihuites</t>
@@ -7596,9 +10151,14 @@
       </c>
     </row>
     <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>El Plateado de Joaquín Amaro</t>
+          <t>El Plateado De Joaquín Amaro</t>
         </is>
       </c>
       <c r="C545">
@@ -7609,6 +10169,11 @@
       </c>
     </row>
     <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B546" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -7622,6 +10187,11 @@
       </c>
     </row>
     <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B547" t="inlineStr">
         <is>
           <t>Genaro Codina</t>
@@ -7635,6 +10205,11 @@
       </c>
     </row>
     <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B548" t="inlineStr">
         <is>
           <t>General Enrique Estrada</t>
@@ -7648,6 +10223,11 @@
       </c>
     </row>
     <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B549" t="inlineStr">
         <is>
           <t>General Francisco R. Murguía</t>
@@ -7661,6 +10241,11 @@
       </c>
     </row>
     <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B550" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -7674,6 +10259,11 @@
       </c>
     </row>
     <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B551" t="inlineStr">
         <is>
           <t>Jalpa</t>
@@ -7687,6 +10277,11 @@
       </c>
     </row>
     <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B552" t="inlineStr">
         <is>
           <t>Juchipila</t>
@@ -7700,6 +10295,11 @@
       </c>
     </row>
     <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B553" t="inlineStr">
         <is>
           <t>Loreto</t>
@@ -7713,6 +10313,11 @@
       </c>
     </row>
     <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B554" t="inlineStr">
         <is>
           <t>Luis Moya</t>
@@ -7726,6 +10331,11 @@
       </c>
     </row>
     <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B555" t="inlineStr">
         <is>
           <t>Miguel Auza</t>
@@ -7739,6 +10349,11 @@
       </c>
     </row>
     <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B556" t="inlineStr">
         <is>
           <t>Momax</t>
@@ -7752,6 +10367,11 @@
       </c>
     </row>
     <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B557" t="inlineStr">
         <is>
           <t>Monte Escobedo</t>
@@ -7765,9 +10385,14 @@
       </c>
     </row>
     <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Nochistlán de Mejía</t>
+          <t>Nochistlán De Mejía</t>
         </is>
       </c>
       <c r="C558">
@@ -7778,6 +10403,11 @@
       </c>
     </row>
     <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B559" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -7791,6 +10421,11 @@
       </c>
     </row>
     <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B560" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -7804,6 +10439,11 @@
       </c>
     </row>
     <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B561" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -7817,6 +10457,11 @@
       </c>
     </row>
     <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B562" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -7830,6 +10475,11 @@
       </c>
     </row>
     <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B563" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -7843,6 +10493,11 @@
       </c>
     </row>
     <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B564" t="inlineStr">
         <is>
           <t>Tepetongo</t>
@@ -7856,19 +10511,29 @@
       </c>
     </row>
     <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C565">
         <v>3</v>
       </c>
       <c r="D565">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B566" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -7882,6 +10547,11 @@
       </c>
     </row>
     <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B567" t="inlineStr">
         <is>
           <t>Vetagrande</t>
@@ -7895,9 +10565,14 @@
       </c>
     </row>
     <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C568">
@@ -7908,6 +10583,11 @@
       </c>
     </row>
     <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B569" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -7921,6 +10601,11 @@
       </c>
     </row>
     <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B570" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -7934,6 +10619,11 @@
       </c>
     </row>
     <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B571" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -7947,6 +10637,11 @@
       </c>
     </row>
     <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B572" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7970,41 +10665,6 @@
       </c>
       <c r="D573">
         <v>1</v>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 566,547</t>
-        </is>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>Mayo de 2023</t>
-        </is>
       </c>
     </row>
   </sheetData>
